--- a/Document 26.09.01/논문 엑셀 자료.xlsx
+++ b/Document 26.09.01/논문 엑셀 자료.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HanPC_2\Documents\Master Degree Thesis\Material csv(26.07.28)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HanPC_2\Documents\Master Degree Thesis\Document 26.09.01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D770C307-56CF-40E8-A9B5-C75E6482BB67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBE63EF-2688-4CB1-BD6F-7A68F9E9B3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4800" yWindow="0" windowWidth="14400" windowHeight="10080" activeTab="1" xr2:uid="{62B0BBA2-F51D-406A-B0A4-2D1F2757D296}"/>
+    <workbookView xWindow="792" yWindow="1020" windowWidth="12468" windowHeight="8988" activeTab="1" xr2:uid="{62B0BBA2-F51D-406A-B0A4-2D1F2757D296}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="물질별 음파 속도, 임피던스" sheetId="2" r:id="rId2"/>
+    <sheet name="왕복 거리 환산1" sheetId="1" r:id="rId1"/>
+    <sheet name="왕복 거리 환산 (온세미)" sheetId="3" r:id="rId2"/>
+    <sheet name="물질별 음파 속도, 임피던스" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="38">
   <si>
     <t>거리</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -613,16 +614,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9EFBFDD-1936-45A7-9B04-F51E64107724}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" customWidth="1"/>
-    <col min="2" max="2" width="19.75" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="19.83203125" customWidth="1"/>
-    <col min="5" max="5" width="19.1640625" customWidth="1"/>
+    <col min="1" max="1" width="22.19921875" customWidth="1"/>
+    <col min="2" max="2" width="19.69921875" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" customWidth="1"/>
+    <col min="4" max="4" width="19.796875" customWidth="1"/>
+    <col min="5" max="5" width="19.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -654,7 +655,7 @@
         <v>36700</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -695,7 +696,7 @@
         <v>18700</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -744,18 +745,151 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EC993ED-FBC3-43CC-B3E5-F7BBA8277F87}">
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="22.19921875" customWidth="1"/>
+    <col min="2" max="2" width="19.69921875" customWidth="1"/>
+    <col min="3" max="3" width="16.69921875" customWidth="1"/>
+    <col min="4" max="4" width="19.796875" customWidth="1"/>
+    <col min="5" max="5" width="19.19921875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>29500</v>
+      </c>
+      <c r="C1">
+        <v>30000</v>
+      </c>
+      <c r="D1">
+        <v>30800</v>
+      </c>
+      <c r="E1">
+        <v>32100</v>
+      </c>
+      <c r="F1">
+        <v>33100</v>
+      </c>
+      <c r="G1">
+        <v>33600</v>
+      </c>
+      <c r="H1">
+        <v>35500</v>
+      </c>
+      <c r="I1">
+        <v>36000</v>
+      </c>
+      <c r="J1">
+        <v>36700</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <f t="shared" ref="B2:J2" si="0">B1-18000</f>
+        <v>11500</v>
+      </c>
+      <c r="C2">
+        <f t="shared" si="0"/>
+        <v>12000</v>
+      </c>
+      <c r="D2">
+        <f t="shared" si="0"/>
+        <v>12800</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>14100</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>15100</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>15600</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>17500</v>
+      </c>
+      <c r="I2">
+        <f t="shared" si="0"/>
+        <v>18000</v>
+      </c>
+      <c r="J2">
+        <f t="shared" si="0"/>
+        <v>18700</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <f t="shared" ref="B3:J3" si="1">B2/1000000000*1501/2 * 1000</f>
+        <v>8.630749999999999</v>
+      </c>
+      <c r="C3" s="1">
+        <f t="shared" si="1"/>
+        <v>9.0060000000000002</v>
+      </c>
+      <c r="D3" s="1">
+        <f t="shared" si="1"/>
+        <v>9.6063999999999989</v>
+      </c>
+      <c r="E3" s="1">
+        <f t="shared" si="1"/>
+        <v>10.582050000000001</v>
+      </c>
+      <c r="F3" s="1">
+        <f t="shared" si="1"/>
+        <v>11.332549999999999</v>
+      </c>
+      <c r="G3" s="1">
+        <f t="shared" si="1"/>
+        <v>11.707799999999999</v>
+      </c>
+      <c r="H3" s="1">
+        <f t="shared" si="1"/>
+        <v>13.133749999999999</v>
+      </c>
+      <c r="I3" s="1">
+        <f t="shared" si="1"/>
+        <v>13.509</v>
+      </c>
+      <c r="J3" s="1">
+        <f t="shared" si="1"/>
+        <v>14.034350000000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CBFA7C3-77D1-4DCA-8D6B-884D2751F22D}">
   <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="16.33203125" customWidth="1"/>
-    <col min="2" max="2" width="21.4140625" customWidth="1"/>
-    <col min="3" max="3" width="18.25" customWidth="1"/>
-    <col min="4" max="4" width="18.9140625" customWidth="1"/>
-    <col min="5" max="5" width="16.9140625" customWidth="1"/>
+    <col min="1" max="1" width="16.296875" customWidth="1"/>
+    <col min="2" max="2" width="21.3984375" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" customWidth="1"/>
+    <col min="4" max="4" width="18.8984375" customWidth="1"/>
+    <col min="5" max="5" width="16.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>3</v>
       </c>
@@ -772,7 +906,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -789,7 +923,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
@@ -806,7 +940,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
@@ -823,7 +957,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="4" t="s">
         <v>22</v>
       </c>
@@ -840,7 +974,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="4" t="s">
         <v>27</v>
       </c>
@@ -857,7 +991,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="28.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:5" ht="28.2" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="4" t="s">
         <v>33</v>
       </c>
@@ -874,50 +1008,50 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="9" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="9" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
-    <row r="10" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
     </row>
-    <row r="11" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="2"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
     </row>
-    <row r="13" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="2"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
     </row>
-    <row r="14" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
     </row>
-    <row r="15" spans="1:5" ht="17.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="15" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
